--- a/Liste des composants.xlsx
+++ b/Liste des composants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mod_loc\Documents\Anael\2025-2026\PROJET 2026 PICO-CENTRALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2614A44-BC8E-40E9-8189-8221EFEB9994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEFB87B-2655-4BA9-A518-0ADC0E8EAECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="750" windowWidth="19440" windowHeight="15600" xr2:uid="{F28EE312-05E0-4F62-B602-6EFCA028A856}"/>
+    <workbookView xWindow="28680" yWindow="750" windowWidth="19440" windowHeight="14880" xr2:uid="{F28EE312-05E0-4F62-B602-6EFCA028A856}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>Ref</t>
   </si>
@@ -141,6 +141,63 @@
   </si>
   <si>
     <t>ROHM</t>
+  </si>
+  <si>
+    <t>nok</t>
+  </si>
+  <si>
+    <t>Ref prof</t>
+  </si>
+  <si>
+    <t>Dejà ok</t>
+  </si>
+  <si>
+    <t>Déjà ok</t>
+  </si>
+  <si>
+    <t>plus sur schéma</t>
+  </si>
+  <si>
+    <t>MCP3021A0T</t>
+  </si>
+  <si>
+    <t>MCP3021A1T</t>
+  </si>
+  <si>
+    <t>FDDD4141</t>
+  </si>
+  <si>
+    <t>C1, C8, C10, C11, C17, C12, C13, C14, C16</t>
+  </si>
+  <si>
+    <t>Vérifier condo</t>
+  </si>
+  <si>
+    <t>Dispo chez farnell, valeur et tension de service</t>
+  </si>
+  <si>
+    <t>Multicomp PRO</t>
+  </si>
+  <si>
+    <t>C10, C11</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C12,C14</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>RUBYCON</t>
+  </si>
+  <si>
+    <t>C1, C13, C16</t>
   </si>
 </sst>
 </file>
@@ -531,13 +588,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3AD702-BEE4-4FE2-A17E-B228C010BF95}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -554,7 +611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -571,7 +628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -588,7 +645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -605,7 +662,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -622,7 +679,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -633,7 +690,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -643,8 +700,14 @@
       <c r="E7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7">
+        <v>4179098</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -660,117 +723,113 @@
       <c r="E8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>3796961</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C10">
+      <c r="C12">
         <v>2848984</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C11">
+      <c r="C13">
         <v>3483076</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C12">
+      <c r="C14">
         <v>1332097</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>3929030</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>27</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>9</v>
@@ -778,21 +837,141 @@
       <c r="E16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C17">
+      <c r="C19">
         <v>1680404</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23">
+        <v>1759483</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>3253941</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>1848452</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27">
+        <v>1144681</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
         <v>29</v>
       </c>
     </row>

--- a/Liste des composants.xlsx
+++ b/Liste des composants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mod_loc\Documents\Anael\2025-2026\PROJET 2026 PICO-CENTRALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEFB87B-2655-4BA9-A518-0ADC0E8EAECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B9CBCA-107E-42F9-BBCD-3F9A43A2E718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="750" windowWidth="19440" windowHeight="14880" xr2:uid="{F28EE312-05E0-4F62-B602-6EFCA028A856}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>Ref</t>
   </si>
@@ -191,13 +191,16 @@
     <t>C12,C14</t>
   </si>
   <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>RUBYCON</t>
-  </si>
-  <si>
     <t>C1, C13, C16</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>KYOCERA AVX</t>
+  </si>
+  <si>
+    <t>KEMET</t>
   </si>
 </sst>
 </file>
@@ -901,7 +904,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
@@ -921,10 +924,10 @@
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C24">
-        <v>3253941</v>
+        <v>197130</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -938,10 +941,10 @@
         <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C25">
-        <v>1848452</v>
+        <v>4312864</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -954,6 +957,15 @@
       <c r="A26" t="s">
         <v>48</v>
       </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26">
+        <v>3873527</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
       <c r="E26" t="s">
         <v>29</v>
       </c>
@@ -963,10 +975,10 @@
         <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27">
-        <v>1144681</v>
+        <v>1432414</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -978,5 +990,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>